--- a/branches/ci/gh-pages-preview/observations-summary.xlsx
+++ b/branches/ci/gh-pages-preview/observations-summary.xlsx
@@ -83,7 +83,7 @@
     <t>MII PR Kardio Atherosklerotisches Erstereignis</t>
   </si>
   <si>
-    <t>null#ae</t>
+    <t>MII CS Kardio Atherosklerotisches Ereignis#ae</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ, instantĵ</t>
@@ -110,7 +110,7 @@
     <t>null#null, null#null, null#null, null#eg-cv</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-sct|2026.0.1 (required)</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-sct|2027.0.0-ballot.rc1 (required)</t>
   </si>
   <si>
     <t>mii-pr-kardio-ekg-annotation</t>
@@ -465,7 +465,7 @@
         <v>23</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>24</v>
